--- a/import/schedule/Расписание.xlsx
+++ b/import/schedule/Расписание.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="1149">
   <si>
     <t>УТВЕРЖДАЮ</t>
   </si>
@@ -3380,6 +3380,93 @@
   </si>
   <si>
     <t>232 История (9) Петренко В.Б.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302/413 Ин.язык (1-15,17) Рахимова А.Л./Сорокина Н.Б.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (14) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/413 Ин.язык (1,4,6,8-11) Кривцова С.Н./Сорокина Н.Б.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/314 Ин.язык (1-10,12,14,16,17) Сорокина Н.Б./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302/409 Ин.язык (1-15,17) Рахимова А.Л./Кривцова С.Н.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/409 Ин.язык (1-9,12) Степаненко О.А./Кривцова С.Н.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (1) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/302 Ин.язык (1-13,15,16) Степаненко О.А./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (13) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (14) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/314 Ин.язык (14) Сорокина Н.Б./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (1-10) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302/413 Ин.язык (1-3,5-12,14-17) Рахимова А.Л./Сорокина Н.Б.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/409 Ин.язык (13) Степаненко О.А./Кривцова С.Н.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/409 Ин.язык (1,3,5-8,10,12,14-17) Степаненко О.А./Кривцова С.Н.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (1-6,8-15) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (1,2,4-7,9-17) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (1,3-7,9,11,12,14,15,17) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (1-3,5-15) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (12) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/413 Ин.язык (1-8,10-14) Степаненко О.А./Сорокина Н.Б.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413/302 Ин.язык (10,11,13) Сорокина Н.Б./Рахимова А.Л.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/409 Ин.язык (1-11,13,14,16) Степаненко О.А./Кривцова С.Н.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (1,3-5,7-9,11-17) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/409 Ин.язык (1-5,7-17) Степаненко О.А./Кривцова С.Н.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (2) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/314 Ин.язык (1,2,4-6,8-17) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409/413 Ин.язык (1-16) Кривцова С.Н./Степаненко О.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314/409 Ин.язык (8,11-13) Степаненко О.А./Кривцова С.Н.</t>
   </si>
 </sst>
 </file>
@@ -5896,7 +5983,7 @@
         <v>75</v>
       </c>
       <c r="X6" s="119" t="s">
-        <v>76</v>
+        <v>1120</v>
       </c>
       <c r="Y6" s="119" t="s">
         <v>77</v>
@@ -5914,7 +6001,7 @@
         <v>81</v>
       </c>
       <c r="AD6" s="119" t="s">
-        <v>82</v>
+        <v>1121</v>
       </c>
       <c r="AE6" s="182"/>
       <c r="AF6" s="119" t="s">
@@ -5936,7 +6023,7 @@
         <v>87</v>
       </c>
       <c r="AL6" s="119" t="s">
-        <v>88</v>
+        <v>1122</v>
       </c>
       <c r="AM6" s="119" t="s">
         <v>89</v>
@@ -6010,9 +6097,7 @@
         <v>103</v>
       </c>
       <c r="W7" s="119"/>
-      <c r="X7" s="119" t="s">
-        <v>104</v>
-      </c>
+      <c r="X7" s="119"/>
       <c r="Y7" s="119"/>
       <c r="Z7" s="124"/>
       <c r="AA7" s="178"/>
@@ -6020,9 +6105,7 @@
       <c r="AC7" s="119" t="s">
         <v>105</v>
       </c>
-      <c r="AD7" s="119" t="s">
-        <v>106</v>
-      </c>
+      <c r="AD7" s="119"/>
       <c r="AE7" s="179"/>
       <c r="AF7" s="178"/>
       <c r="AG7" s="178"/>
@@ -6032,9 +6115,7 @@
       <c r="AK7" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="AL7" s="119" t="s">
-        <v>108</v>
-      </c>
+      <c r="AL7" s="119"/>
       <c r="AM7" s="119" t="s">
         <v>109</v>
       </c>
@@ -6438,13 +6519,13 @@
         <v>124</v>
       </c>
       <c r="T14" s="122" t="s">
-        <v>125</v>
+        <v>1123</v>
       </c>
       <c r="U14" s="140" t="s">
         <v>126</v>
       </c>
       <c r="V14" s="120" t="s">
-        <v>76</v>
+        <v>1124</v>
       </c>
       <c r="W14" s="119" t="s">
         <v>127</v>
@@ -6489,7 +6570,7 @@
         <v>137</v>
       </c>
       <c r="AK14" s="119" t="s">
-        <v>138</v>
+        <v>1125</v>
       </c>
       <c r="AL14" s="119" t="s">
         <v>139</v>
@@ -6560,13 +6641,9 @@
       </c>
       <c r="R15" s="178"/>
       <c r="S15" s="178"/>
-      <c r="T15" s="122" t="s">
-        <v>155</v>
-      </c>
+      <c r="T15" s="122"/>
       <c r="U15" s="119"/>
-      <c r="V15" s="120" t="s">
-        <v>156</v>
-      </c>
+      <c r="V15" s="120"/>
       <c r="W15" s="119"/>
       <c r="X15" s="119"/>
       <c r="Y15" s="119"/>
@@ -6585,9 +6662,7 @@
       <c r="AH15" s="178"/>
       <c r="AI15" s="178"/>
       <c r="AJ15" s="178"/>
-      <c r="AK15" s="119" t="s">
-        <v>159</v>
-      </c>
+      <c r="AK15" s="119"/>
       <c r="AL15" s="178"/>
       <c r="AM15" s="178"/>
       <c r="AN15" s="141"/>
@@ -8166,7 +8241,7 @@
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
       <c r="O39" s="119" t="s">
-        <v>300</v>
+        <v>1126</v>
       </c>
       <c r="P39" s="119"/>
       <c r="Q39" s="119"/>
@@ -8230,9 +8305,7 @@
       <c r="L40" s="120"/>
       <c r="M40" s="120"/>
       <c r="N40" s="123"/>
-      <c r="O40" s="120" t="s">
-        <v>305</v>
-      </c>
+      <c r="O40" s="120"/>
       <c r="P40" s="123"/>
       <c r="Q40" s="169"/>
       <c r="R40" s="141"/>
@@ -9537,7 +9610,7 @@
         <v>2</v>
       </c>
       <c r="C62" s="164" t="s">
-        <v>358</v>
+        <v>1127</v>
       </c>
       <c r="D62" s="169" t="s">
         <v>308</v>
@@ -9685,9 +9758,7 @@
     <row r="63" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="194"/>
       <c r="B63" s="191"/>
-      <c r="C63" s="164" t="s">
-        <v>387</v>
-      </c>
+      <c r="C63" s="164"/>
       <c r="D63" s="169"/>
       <c r="E63" s="198"/>
       <c r="F63" s="169" t="s">
@@ -9736,10 +9807,10 @@
       <c r="AK63" s="178"/>
       <c r="AL63" s="120"/>
       <c r="AM63" s="120" t="s">
-        <v>393</v>
+        <v>1128</v>
       </c>
       <c r="AN63" s="141" t="s">
-        <v>394</v>
+        <v>1129</v>
       </c>
       <c r="AO63" s="178"/>
       <c r="AP63" s="178"/>
@@ -9802,12 +9873,8 @@
       <c r="AJ64" s="179"/>
       <c r="AK64" s="179"/>
       <c r="AL64" s="120"/>
-      <c r="AM64" s="120" t="s">
-        <v>398</v>
-      </c>
-      <c r="AN64" s="141" t="s">
-        <v>399</v>
-      </c>
+      <c r="AM64" s="120"/>
+      <c r="AN64" s="141"/>
       <c r="AO64" s="179"/>
       <c r="AP64" s="179"/>
       <c r="AQ64" s="179"/>
@@ -10245,7 +10312,7 @@
         <v>421</v>
       </c>
       <c r="AJ71" s="119" t="s">
-        <v>422</v>
+        <v>1131</v>
       </c>
       <c r="AK71" s="119" t="s">
         <v>423</v>
@@ -10359,9 +10426,7 @@
       <c r="AI72" s="119" t="s">
         <v>445</v>
       </c>
-      <c r="AJ72" s="119" t="s">
-        <v>446</v>
-      </c>
+      <c r="AJ72" s="119"/>
       <c r="AK72" s="178"/>
       <c r="AL72" s="119" t="s">
         <v>447</v>
@@ -10437,7 +10502,7 @@
       <c r="AD73" s="179"/>
       <c r="AE73" s="179"/>
       <c r="AF73" s="119" t="s">
-        <v>82</v>
+        <v>1130</v>
       </c>
       <c r="AG73" s="119"/>
       <c r="AH73" s="178"/>
@@ -10491,9 +10556,7 @@
       <c r="AC74" s="179"/>
       <c r="AD74" s="179"/>
       <c r="AE74" s="179"/>
-      <c r="AF74" s="119" t="s">
-        <v>399</v>
-      </c>
+      <c r="AF74" s="119"/>
       <c r="AG74" s="120"/>
       <c r="AH74" s="179"/>
       <c r="AI74" s="179"/>
@@ -10788,7 +10851,7 @@
         <v>458</v>
       </c>
       <c r="D80" s="168" t="s">
-        <v>459</v>
+        <v>1132</v>
       </c>
       <c r="E80" s="133" t="s">
         <v>59</v>
@@ -10869,7 +10932,7 @@
         <v>481</v>
       </c>
       <c r="AE80" s="119" t="s">
-        <v>398</v>
+        <v>1133</v>
       </c>
       <c r="AF80" s="119"/>
       <c r="AG80" s="119" t="s">
@@ -10894,7 +10957,7 @@
         <v>484</v>
       </c>
       <c r="AN80" s="120" t="s">
-        <v>485</v>
+        <v>1134</v>
       </c>
       <c r="AO80" s="141" t="s">
         <v>486</v>
@@ -10936,9 +10999,7 @@
       <c r="C81" s="164" t="s">
         <v>493</v>
       </c>
-      <c r="D81" s="168" t="s">
-        <v>494</v>
-      </c>
+      <c r="D81" s="168"/>
       <c r="E81" s="189"/>
       <c r="F81" s="168" t="s">
         <v>495</v>
@@ -10995,9 +11056,7 @@
         <v>248</v>
       </c>
       <c r="AD81" s="178"/>
-      <c r="AE81" s="119" t="s">
-        <v>393</v>
-      </c>
+      <c r="AE81" s="119"/>
       <c r="AF81" s="120"/>
       <c r="AG81" s="119" t="s">
         <v>508</v>
@@ -11012,9 +11071,7 @@
       <c r="AK81" s="178"/>
       <c r="AL81" s="178"/>
       <c r="AM81" s="141"/>
-      <c r="AN81" s="120" t="s">
-        <v>510</v>
-      </c>
+      <c r="AN81" s="120"/>
       <c r="AO81" s="141"/>
       <c r="AP81" s="120" t="s">
         <v>511</v>
@@ -12607,7 +12664,7 @@
         <v>569</v>
       </c>
       <c r="AG108" s="119" t="s">
-        <v>570</v>
+        <v>1135</v>
       </c>
       <c r="AH108" s="119" t="s">
         <v>571</v>
@@ -12713,9 +12770,7 @@
       </c>
       <c r="AE109" s="178"/>
       <c r="AF109" s="177"/>
-      <c r="AG109" s="119" t="s">
-        <v>594</v>
-      </c>
+      <c r="AG109" s="119"/>
       <c r="AH109" s="178"/>
       <c r="AI109" s="178"/>
       <c r="AJ109" s="124" t="s">
@@ -13719,7 +13774,7 @@
         <v>168</v>
       </c>
       <c r="N125" s="122" t="s">
-        <v>640</v>
+        <v>1136</v>
       </c>
       <c r="O125" s="119" t="s">
         <v>124</v>
@@ -13851,9 +13906,7 @@
       <c r="K126" s="178"/>
       <c r="L126" s="123"/>
       <c r="M126" s="181"/>
-      <c r="N126" s="122" t="s">
-        <v>665</v>
-      </c>
+      <c r="N126" s="122"/>
       <c r="O126" s="178"/>
       <c r="P126" s="181"/>
       <c r="Q126" s="178"/>
@@ -14311,7 +14364,7 @@
         <v>692</v>
       </c>
       <c r="AD133" s="119" t="s">
-        <v>693</v>
+        <v>1137</v>
       </c>
       <c r="AE133" s="119" t="s">
         <v>418</v>
@@ -14439,9 +14492,7 @@
       </c>
       <c r="AB134" s="179"/>
       <c r="AC134" s="178"/>
-      <c r="AD134" s="119" t="s">
-        <v>721</v>
-      </c>
+      <c r="AD134" s="119"/>
       <c r="AE134" s="178"/>
       <c r="AF134" s="119" t="s">
         <v>722</v>
@@ -15849,7 +15900,7 @@
       </c>
       <c r="O158" s="182"/>
       <c r="P158" s="122" t="s">
-        <v>767</v>
+        <v>1138</v>
       </c>
       <c r="Q158" s="122" t="s">
         <v>768</v>
@@ -15895,7 +15946,7 @@
         <v>373</v>
       </c>
       <c r="AF158" s="119" t="s">
-        <v>777</v>
+        <v>1140</v>
       </c>
       <c r="AG158" s="119" t="s">
         <v>778</v>
@@ -15975,9 +16026,7 @@
         <v>212</v>
       </c>
       <c r="O159" s="179"/>
-      <c r="P159" s="122" t="s">
-        <v>789</v>
-      </c>
+      <c r="P159" s="122"/>
       <c r="Q159" s="181"/>
       <c r="R159" s="120" t="s">
         <v>790</v>
@@ -15993,7 +16042,7 @@
         <v>792</v>
       </c>
       <c r="Y159" s="119" t="s">
-        <v>793</v>
+        <v>1139</v>
       </c>
       <c r="Z159" s="133" t="s">
         <v>794</v>
@@ -16005,9 +16054,7 @@
       </c>
       <c r="AD159" s="120"/>
       <c r="AE159" s="178"/>
-      <c r="AF159" s="119" t="s">
-        <v>795</v>
-      </c>
+      <c r="AF159" s="119"/>
       <c r="AG159" s="119"/>
       <c r="AH159" s="120"/>
       <c r="AI159" s="120"/>
@@ -16073,9 +16120,7 @@
       <c r="X160" s="119" t="s">
         <v>801</v>
       </c>
-      <c r="Y160" s="119" t="s">
-        <v>802</v>
-      </c>
+      <c r="Y160" s="119"/>
       <c r="Z160" s="119"/>
       <c r="AA160" s="179"/>
       <c r="AB160" s="179"/>
@@ -17012,7 +17057,7 @@
         <v>842</v>
       </c>
       <c r="AE174" s="119" t="s">
-        <v>843</v>
+        <v>1142</v>
       </c>
       <c r="AF174" s="119" t="s">
         <v>84</v>
@@ -17124,7 +17169,7 @@
         <v>162</v>
       </c>
       <c r="Z175" s="119" t="s">
-        <v>864</v>
+        <v>1141</v>
       </c>
       <c r="AA175" s="178"/>
       <c r="AB175" s="178"/>
@@ -17132,9 +17177,7 @@
         <v>865</v>
       </c>
       <c r="AD175" s="178"/>
-      <c r="AE175" s="119" t="s">
-        <v>866</v>
-      </c>
+      <c r="AE175" s="119"/>
       <c r="AF175" s="119"/>
       <c r="AG175" s="119"/>
       <c r="AH175" s="119"/>
@@ -17202,9 +17245,7 @@
       </c>
       <c r="X176" s="120"/>
       <c r="Y176" s="119"/>
-      <c r="Z176" s="119" t="s">
-        <v>598</v>
-      </c>
+      <c r="Z176" s="119"/>
       <c r="AA176" s="179"/>
       <c r="AB176" s="179"/>
       <c r="AC176" s="178"/>
@@ -19071,7 +19112,7 @@
         <v>565</v>
       </c>
       <c r="AA207" s="119" t="s">
-        <v>951</v>
+        <v>1143</v>
       </c>
       <c r="AB207" s="119" t="s">
         <v>370</v>
@@ -19181,9 +19222,7 @@
       </c>
       <c r="Y208" s="119"/>
       <c r="Z208" s="119"/>
-      <c r="AA208" s="119" t="s">
-        <v>968</v>
-      </c>
+      <c r="AA208" s="119"/>
       <c r="AB208" s="178"/>
       <c r="AC208" s="120" t="s">
         <v>281</v>
@@ -19550,7 +19589,7 @@
         <v>126</v>
       </c>
       <c r="W214" s="119" t="s">
-        <v>980</v>
+        <v>1144</v>
       </c>
       <c r="X214" s="120" t="s">
         <v>180</v>
@@ -19672,9 +19711,7 @@
       <c r="T215" s="120"/>
       <c r="U215" s="178"/>
       <c r="V215" s="178"/>
-      <c r="W215" s="119" t="s">
-        <v>1001</v>
-      </c>
+      <c r="W215" s="119"/>
       <c r="X215" s="120"/>
       <c r="Y215" s="119"/>
       <c r="Z215" s="119" t="s">
@@ -19713,7 +19750,7 @@
       </c>
       <c r="AP215" s="178"/>
       <c r="AQ215" s="119" t="s">
-        <v>296</v>
+        <v>1145</v>
       </c>
       <c r="AR215" s="178"/>
       <c r="AS215" s="120"/>
@@ -19775,9 +19812,7 @@
         <v>1011</v>
       </c>
       <c r="AP216" s="179"/>
-      <c r="AQ216" s="119" t="s">
-        <v>236</v>
-      </c>
+      <c r="AQ216" s="119"/>
       <c r="AR216" s="179"/>
       <c r="AS216" s="120"/>
       <c r="AT216" s="179"/>
@@ -20136,7 +20171,7 @@
         <v>1028</v>
       </c>
       <c r="AC222" s="119" t="s">
-        <v>1029</v>
+        <v>1146</v>
       </c>
       <c r="AD222" s="119" t="s">
         <v>1030</v>
@@ -20262,9 +20297,7 @@
       <c r="AB223" s="119" t="s">
         <v>1050</v>
       </c>
-      <c r="AC223" s="119" t="s">
-        <v>1051</v>
-      </c>
+      <c r="AC223" s="119"/>
       <c r="AD223" s="178"/>
       <c r="AE223" s="177" t="s">
         <v>1052</v>
@@ -20676,7 +20709,7 @@
         <v>1069</v>
       </c>
       <c r="Q230" s="122" t="s">
-        <v>1070</v>
+        <v>1147</v>
       </c>
       <c r="R230" s="119" t="s">
         <v>1071</v>
@@ -20709,7 +20742,7 @@
         <v>300</v>
       </c>
       <c r="AB230" s="119" t="s">
-        <v>1077</v>
+        <v>1148</v>
       </c>
       <c r="AC230" s="120" t="s">
         <v>1078</v>
@@ -20804,9 +20837,7 @@
       <c r="P231" s="119" t="s">
         <v>1092</v>
       </c>
-      <c r="Q231" s="122" t="s">
-        <v>1093</v>
-      </c>
+      <c r="Q231" s="122"/>
       <c r="R231" s="178"/>
       <c r="S231" s="178"/>
       <c r="T231" s="178"/>
@@ -20823,9 +20854,7 @@
       <c r="AA231" s="119" t="s">
         <v>1095</v>
       </c>
-      <c r="AB231" s="119" t="s">
-        <v>1096</v>
-      </c>
+      <c r="AB231" s="119"/>
       <c r="AC231" s="120" t="s">
         <v>1057</v>
       </c>
@@ -21873,7 +21902,7 @@
       <c r="AV252" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="796">
+  <mergeCells count="825">
     <mergeCell ref="B230:B237"/>
     <mergeCell ref="AD216:AD220"/>
     <mergeCell ref="L90:L93"/>
@@ -22670,6 +22699,35 @@
     <mergeCell ref="AV15:AV18"/>
     <mergeCell ref="AQ25:AQ29"/>
     <mergeCell ref="P81:P85"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="AD6:AD7"/>
+    <mergeCell ref="AL6:AL7"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="AK14:AK15"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="AM63:AM64"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AF73:AF74"/>
+    <mergeCell ref="AJ71:AJ72"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="AE80:AE81"/>
+    <mergeCell ref="AN80:AN81"/>
+    <mergeCell ref="AG108:AG109"/>
+    <mergeCell ref="N125:N126"/>
+    <mergeCell ref="AD133:AD134"/>
+    <mergeCell ref="P158:P159"/>
+    <mergeCell ref="Y159:Y160"/>
+    <mergeCell ref="AF158:AF159"/>
+    <mergeCell ref="Z175:Z176"/>
+    <mergeCell ref="AE174:AE175"/>
+    <mergeCell ref="AA207:AA208"/>
+    <mergeCell ref="W214:W215"/>
+    <mergeCell ref="AQ215:AQ216"/>
+    <mergeCell ref="AC222:AC223"/>
+    <mergeCell ref="Q230:Q231"/>
+    <mergeCell ref="AB230:AB231"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/import/schedule/Расписание.xlsx
+++ b/import/schedule/Расписание.xlsx
@@ -3477,9 +3477,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -3493,10 +3492,9 @@
       <b/>
       <sz val="48"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3517,36 +3515,32 @@
     <font>
       <sz val="55"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3559,10 +3553,9 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -5374,7 +5367,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Times New Roman"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5408,7 +5401,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Times New Roman"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/import/schedule/Расписание.xlsx
+++ b/import/schedule/Расписание.xlsx
@@ -14972,7 +14972,11 @@
       <c r="I144" s="120"/>
       <c r="J144" s="181"/>
       <c r="K144" s="181"/>
-      <c r="L144" s="253"/>
+      <c r="L144" s="253" t="inlineStr">
+        <is>
+          <t>418 Биология (8,9) Боброва О.В.</t>
+        </is>
+      </c>
       <c r="M144" s="180"/>
       <c r="N144" s="181"/>
       <c r="O144" s="181"/>
